--- a/Religion_In_Canada.xlsx
+++ b/Religion_In_Canada.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/A07FE6C8272E308A/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a07fe6c8272e308a/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="978" documentId="8_{D42A7CC2-2197-4767-BD5B-9380ECC740E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63A55CDD-CE1B-41EB-932A-396A78599081}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{E4D3A6A5-3925-412D-B440-607F83809EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07883784-3106-403C-9836-D2E614CCB5AA}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{F2E6CCFD-35CF-4578-A6E2-42BEC15B5205}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="4" xr2:uid="{F2E6CCFD-35CF-4578-A6E2-42BEC15B5205}"/>
   </bookViews>
   <sheets>
     <sheet name="Manitoba" sheetId="1" r:id="rId1"/>
     <sheet name="Ontario" sheetId="2" r:id="rId2"/>
     <sheet name="Quebec" sheetId="3" r:id="rId3"/>
+    <sheet name="New Brunswick" sheetId="4" r:id="rId4"/>
+    <sheet name="PEI" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Manitoba!$A$1:$D$27</definedName>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="61">
   <si>
     <t xml:space="preserve">Religion   </t>
   </si>
@@ -213,6 +215,18 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>Orthodox*</t>
+  </si>
+  <si>
+    <t>*: n.o.s + Eastern Orthodox</t>
+  </si>
+  <si>
+    <t>New Brunswick</t>
+  </si>
+  <si>
+    <t>Prince Edward Island</t>
+  </si>
 </sst>
 </file>
 
@@ -312,13 +326,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1667,77 +1681,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="F1" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="F1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="K1" s="16" t="s">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="K1" s="17" t="s">
         <v>22</v>
       </c>
       <c r="L1" s="15"/>
       <c r="M1" s="15"/>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
       <c r="R1" s="7"/>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
       <c r="V1" s="7"/>
-      <c r="W1" s="16" t="s">
+      <c r="W1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="AA1" s="16" t="s">
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="AA1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AE1" s="16" t="s">
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AE1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AI1" s="16" t="s">
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AI1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
-      <c r="AM1" s="16" t="s">
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AM1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="16"/>
-      <c r="AO1" s="16"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
       <c r="AS1" s="15"/>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>2021</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="F2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="F2" s="16">
         <v>2021</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
       <c r="K2" s="15">
         <v>2021</v>
       </c>
@@ -1783,17 +1797,17 @@
       <c r="AS2" s="15"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
       <c r="D3" s="1"/>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
       <c r="I3" s="1"/>
       <c r="K3" s="15" t="s">
         <v>29</v>
@@ -3434,23 +3448,6 @@
     <sortCondition descending="1" ref="AN23"/>
   </sortState>
   <mergeCells count="33">
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AI3:AK3"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="O3:Q3"/>
     <mergeCell ref="AQ1:AS1"/>
     <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="AQ3:AS3"/>
@@ -3467,6 +3464,23 @@
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AI1:AK1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AI3:AK3"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AM3:AO3"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B4 B28:B1048576">
     <cfRule type="colorScale" priority="52">
@@ -3637,27 +3651,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W23">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3681,17 +3695,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA5:AA23">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3737,37 +3751,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE5:AE23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3803,37 +3817,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI5:AI23">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3881,57 +3895,57 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM23">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4028,38 +4042,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>2021</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
       <c r="X2" s="12"/>
       <c r="Y2" s="12"/>
       <c r="Z2" s="12"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="15" t="s">
         <v>39</v>
       </c>
@@ -5617,17 +5631,17 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5651,27 +5665,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K23">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5695,6 +5709,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M23">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -5706,26 +5740,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5803,37 +5817,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5857,37 +5871,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S23">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5923,47 +5937,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U23">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6017,37 +6031,37 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6077,10 +6091,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F3FDC6D-4595-40C3-AED4-37F6679FE0B6}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16.88671875" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
@@ -6088,33 +6102,75 @@
     <col min="6" max="6" width="10.33203125" customWidth="1"/>
     <col min="7" max="7" width="17.5546875" customWidth="1"/>
     <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" customWidth="1"/>
+    <col min="16" max="16" width="16.77734375" customWidth="1"/>
+    <col min="17" max="17" width="17.88671875" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" customWidth="1"/>
+    <col min="19" max="19" width="18.21875" customWidth="1"/>
+    <col min="20" max="20" width="16.5546875" customWidth="1"/>
+    <col min="21" max="21" width="17.6640625" customWidth="1"/>
+    <col min="22" max="22" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B1" s="15"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="15"/>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="18"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="15" t="s">
         <v>48</v>
       </c>
       <c r="H3" s="15"/>
+      <c r="I3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -6139,8 +6195,50 @@
       <c r="H4" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -6165,8 +6263,50 @@
       <c r="H5" s="4">
         <v>574850</v>
       </c>
+      <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="4">
+        <v>481595</v>
+      </c>
+      <c r="K5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="4">
+        <v>492155</v>
+      </c>
+      <c r="M5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4">
+        <v>595085</v>
+      </c>
+      <c r="O5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>892005</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4">
+        <v>1254610</v>
+      </c>
+      <c r="S5" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="4">
+        <v>4101385</v>
+      </c>
+      <c r="U5" t="s">
+        <v>6</v>
+      </c>
+      <c r="V5" s="4">
+        <v>333325</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -6191,8 +6331,50 @@
       <c r="H6" s="4">
         <v>419885</v>
       </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4">
+        <v>363385</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="4">
+        <v>377445</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="4">
+        <v>224135</v>
+      </c>
+      <c r="O6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="4">
+        <v>160955</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="4">
+        <v>140740</v>
+      </c>
+      <c r="S6" t="s">
+        <v>14</v>
+      </c>
+      <c r="T6" s="4">
+        <v>1946040</v>
+      </c>
+      <c r="U6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V6" s="4">
+        <v>253330</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -6217,8 +6399,50 @@
       <c r="H7" s="4">
         <v>152155</v>
       </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="4">
+        <v>64285</v>
+      </c>
+      <c r="K7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="4">
+        <v>74910</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" s="4">
+        <v>58215</v>
+      </c>
+      <c r="O7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="4">
+        <v>27620</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>15</v>
+      </c>
+      <c r="R7">
+        <v>22040</v>
+      </c>
+      <c r="S7" t="s">
+        <v>13</v>
+      </c>
+      <c r="T7" s="4">
+        <v>131915</v>
+      </c>
+      <c r="U7" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="4">
+        <v>252450</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -6243,8 +6467,50 @@
       <c r="H8" s="4">
         <v>79165</v>
       </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>11775</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>19790</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8">
+        <v>24455</v>
+      </c>
+      <c r="O8" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8">
+        <v>15100</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="4">
+        <v>21635</v>
+      </c>
+      <c r="S8" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="4">
+        <v>61360</v>
+      </c>
+      <c r="U8" t="s">
+        <v>57</v>
+      </c>
+      <c r="V8">
+        <v>74090</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6269,8 +6535,50 @@
       <c r="H9" s="4">
         <v>57340</v>
       </c>
+      <c r="I9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="4">
+        <v>11090</v>
+      </c>
+      <c r="K9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="4">
+        <v>8800</v>
+      </c>
+      <c r="M9" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="4">
+        <v>8430</v>
+      </c>
+      <c r="O9" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="4">
+        <v>9060</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="4">
+        <v>16035</v>
+      </c>
+      <c r="S9" t="s">
+        <v>15</v>
+      </c>
+      <c r="T9">
+        <v>54555</v>
+      </c>
+      <c r="U9" t="s">
+        <v>16</v>
+      </c>
+      <c r="V9" s="4">
+        <v>39310</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -6295,8 +6603,50 @@
       <c r="H10" s="4">
         <v>37640</v>
       </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="4">
+        <v>9170</v>
+      </c>
+      <c r="K10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" s="4">
+        <v>7695</v>
+      </c>
+      <c r="M10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="4">
+        <v>8200</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="4">
+        <v>8485</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>13</v>
+      </c>
+      <c r="R10" s="4">
+        <v>16010</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="4">
+        <v>48245</v>
+      </c>
+      <c r="U10" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="4">
+        <v>30815</v>
+      </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -6321,8 +6671,50 @@
       <c r="H11" s="4">
         <v>34500</v>
       </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5970</v>
+      </c>
+      <c r="K11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4">
+        <v>7565</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="4">
+        <v>6600</v>
+      </c>
+      <c r="O11" t="s">
+        <v>5</v>
+      </c>
+      <c r="P11" s="4">
+        <v>8410</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" s="4">
+        <v>8850</v>
+      </c>
+      <c r="S11" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="4">
+        <v>20175</v>
+      </c>
+      <c r="U11" t="s">
+        <v>7</v>
+      </c>
+      <c r="V11" s="4">
+        <v>24105</v>
+      </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -6347,8 +6739,50 @@
       <c r="H12">
         <v>31780</v>
       </c>
+      <c r="I12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="4">
+        <v>5965</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="4">
+        <v>6305</v>
+      </c>
+      <c r="M12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="4">
+        <v>4930</v>
+      </c>
+      <c r="O12" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="4">
+        <v>5260</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" s="4">
+        <v>8825</v>
+      </c>
+      <c r="S12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T12" s="4">
+        <v>20115</v>
+      </c>
+      <c r="U12" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="4">
+        <v>21725</v>
+      </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -6373,8 +6807,50 @@
       <c r="H13" s="4">
         <v>21745</v>
       </c>
+      <c r="I13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="4">
+        <v>4620</v>
+      </c>
+      <c r="K13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="4">
+        <v>5370</v>
+      </c>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
+      <c r="N13" s="4">
+        <v>4770</v>
+      </c>
+      <c r="O13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P13" s="4">
+        <v>4665</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="4">
+        <v>7365</v>
+      </c>
+      <c r="S13" t="s">
+        <v>4</v>
+      </c>
+      <c r="T13" s="4">
+        <v>18370</v>
+      </c>
+      <c r="U13" t="s">
+        <v>4</v>
+      </c>
+      <c r="V13" s="4">
+        <v>12960</v>
+      </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -6399,8 +6875,50 @@
       <c r="H14" s="4">
         <v>21105</v>
       </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="4">
+        <v>4365</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="4">
+        <v>5015</v>
+      </c>
+      <c r="M14" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="4">
+        <v>4650</v>
+      </c>
+      <c r="O14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="4">
+        <v>4590</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="4">
+        <v>5520</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" s="4">
+        <v>17360</v>
+      </c>
+      <c r="U14" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" s="4">
+        <v>8580</v>
+      </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -6425,8 +6943,50 @@
       <c r="H15" s="4">
         <v>16085</v>
       </c>
+      <c r="I15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="4">
+        <v>3385</v>
+      </c>
+      <c r="K15" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>4120</v>
+      </c>
+      <c r="M15" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="4">
+        <v>3655</v>
+      </c>
+      <c r="O15" t="s">
+        <v>7</v>
+      </c>
+      <c r="P15" s="4">
+        <v>3970</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>16</v>
+      </c>
+      <c r="R15" s="4">
+        <v>4940</v>
+      </c>
+      <c r="S15" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="4">
+        <v>16140</v>
+      </c>
+      <c r="U15" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="4">
+        <v>7055</v>
+      </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -6451,8 +7011,50 @@
       <c r="H16" s="4">
         <v>14195</v>
       </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="4">
+        <v>2545</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" s="4">
+        <v>3060</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="4">
+        <v>2005</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="4">
+        <v>3610</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>7</v>
+      </c>
+      <c r="R16" s="4">
+        <v>4155</v>
+      </c>
+      <c r="S16" t="s">
+        <v>7</v>
+      </c>
+      <c r="T16" s="4">
+        <v>12570</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V16" s="4">
+        <v>6615</v>
+      </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -6477,8 +7079,50 @@
       <c r="H17" s="4">
         <v>13800</v>
       </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1040</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1435</v>
+      </c>
+      <c r="M17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="4">
+        <v>1915</v>
+      </c>
+      <c r="O17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1405</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>17</v>
+      </c>
+      <c r="R17" s="4">
+        <v>2745</v>
+      </c>
+      <c r="S17" t="s">
+        <v>17</v>
+      </c>
+      <c r="T17" s="4">
+        <v>4945</v>
+      </c>
+      <c r="U17" t="s">
+        <v>17</v>
+      </c>
+      <c r="V17" s="4">
+        <v>2685</v>
+      </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -6503,8 +7147,50 @@
       <c r="H18" s="4">
         <v>7955</v>
       </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="5">
+        <v>580</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="5">
+        <v>900</v>
+      </c>
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" s="5">
+        <v>995</v>
+      </c>
+      <c r="O18" t="s">
+        <v>17</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1305</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="4">
+        <v>1815</v>
+      </c>
+      <c r="S18" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" s="4">
+        <v>4090</v>
+      </c>
+      <c r="U18" t="s">
+        <v>10</v>
+      </c>
+      <c r="V18" s="4">
+        <v>2255</v>
+      </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -6529,8 +7215,50 @@
       <c r="H19" s="4">
         <v>7300</v>
       </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="5">
+        <v>575</v>
+      </c>
+      <c r="K19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="5">
+        <v>690</v>
+      </c>
+      <c r="M19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N19" s="5">
+        <v>670</v>
+      </c>
+      <c r="O19" t="s">
+        <v>10</v>
+      </c>
+      <c r="P19" s="5">
+        <v>925</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" s="4">
+        <v>1495</v>
+      </c>
+      <c r="S19" t="s">
+        <v>20</v>
+      </c>
+      <c r="T19" s="4">
+        <v>3740</v>
+      </c>
+      <c r="U19" t="s">
+        <v>21</v>
+      </c>
+      <c r="V19" s="3">
+        <v>2045</v>
+      </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -6555,8 +7283,50 @@
       <c r="H20" s="4">
         <v>5680</v>
       </c>
+      <c r="I20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="5">
+        <v>530</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="5">
+        <v>560</v>
+      </c>
+      <c r="M20" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="5">
+        <v>510</v>
+      </c>
+      <c r="O20" t="s">
+        <v>12</v>
+      </c>
+      <c r="P20" s="5">
+        <v>515</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>12</v>
+      </c>
+      <c r="R20" s="5">
+        <v>705</v>
+      </c>
+      <c r="S20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" s="4">
+        <v>2985</v>
+      </c>
+      <c r="U20" t="s">
+        <v>12</v>
+      </c>
+      <c r="V20" s="4">
+        <v>1350</v>
+      </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -6581,8 +7351,50 @@
       <c r="H21" s="4">
         <v>4225</v>
       </c>
+      <c r="I21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="5">
+        <v>325</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="5">
+        <v>425</v>
+      </c>
+      <c r="M21" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="5">
+        <v>465</v>
+      </c>
+      <c r="O21" t="s">
+        <v>20</v>
+      </c>
+      <c r="P21" s="5">
+        <v>375</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" s="5">
+        <v>210</v>
+      </c>
+      <c r="S21" t="s">
+        <v>10</v>
+      </c>
+      <c r="T21" s="4">
+        <v>2350</v>
+      </c>
+      <c r="U21" t="s">
+        <v>18</v>
+      </c>
+      <c r="V21" s="5">
+        <v>540</v>
+      </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -6607,8 +7419,50 @@
       <c r="H22" s="4">
         <v>2380</v>
       </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="5">
+        <v>160</v>
+      </c>
+      <c r="K22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="5">
+        <v>155</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="5">
+        <v>190</v>
+      </c>
+      <c r="O22" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="5">
+        <v>125</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="5">
+        <v>160</v>
+      </c>
+      <c r="S22" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="5">
+        <v>550</v>
+      </c>
+      <c r="U22" t="s">
+        <v>11</v>
+      </c>
+      <c r="V22" s="5">
+        <v>80</v>
+      </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -6633,19 +7487,621 @@
       <c r="H23" s="4">
         <v>1870</v>
       </c>
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="5">
+        <v>70</v>
+      </c>
+      <c r="K23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="5">
+        <v>90</v>
+      </c>
+      <c r="M23" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23" s="5">
+        <v>55</v>
+      </c>
+      <c r="O23" t="s">
+        <v>11</v>
+      </c>
+      <c r="P23" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>11</v>
+      </c>
+      <c r="R23" s="5">
+        <v>115</v>
+      </c>
+      <c r="S23" t="s">
+        <v>11</v>
+      </c>
+      <c r="T23" s="5">
+        <v>435</v>
+      </c>
+      <c r="U23" t="s">
+        <v>20</v>
+      </c>
+      <c r="V23" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="T25" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G5:H23">
-    <sortCondition descending="1" ref="H5:H23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="U5:V23">
+    <sortCondition descending="1" ref="V23"/>
   </sortState>
-  <mergeCells count="5">
+  <mergeCells count="12">
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
+  <conditionalFormatting sqref="A4:B23">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 A5:A11 A13:A23">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C23">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D23">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E23">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F4 E8:F8 E5:E7 E9:E23">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F23">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G23">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:H23">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I23">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:I11 I13:I20 I22:I23 I5:K5 I12:K12 K6:K11 I21:K21 K13:K20 K22:K23">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J23">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K23">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:L23">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L8">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M23">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:N23">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O23">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:P23">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q23">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:R23">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:S23">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -6656,8 +8112,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -6669,19 +8153,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B23">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C23">
+  <conditionalFormatting sqref="S5:T23">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6693,31 +8165,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:C23">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D23">
+  <conditionalFormatting sqref="U5:U23">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6728,8 +8176,16 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E23">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6740,20 +8196,26 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E23">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6764,20 +8226,16 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:F4 E8:F8 E5:E7 E9:E23">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G23">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6788,28 +8246,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5:H23">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6821,7 +8257,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:F23">
+  <conditionalFormatting sqref="U5:V23">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6836,4 +8272,4669 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE80984-E5FE-4A85-A6AD-A8165CC8D7B2}">
+  <dimension ref="A1:V23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="21" width="16.77734375" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="15"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="15"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4">
+        <v>305520</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4">
+        <v>146135</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4">
+        <v>159385</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="4">
+        <v>31125</v>
+      </c>
+      <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="4">
+        <v>39520</v>
+      </c>
+      <c r="K5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="4">
+        <v>35275</v>
+      </c>
+      <c r="M5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4">
+        <v>43490</v>
+      </c>
+      <c r="O5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>60785</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4">
+        <v>84030</v>
+      </c>
+      <c r="S5" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="4">
+        <v>293560</v>
+      </c>
+      <c r="U5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V5" s="3">
+        <v>10910</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4">
+        <v>225125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4">
+        <v>120460</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4">
+        <v>104660</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="4">
+        <v>26995</v>
+      </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4">
+        <v>24730</v>
+      </c>
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4">
+        <v>32930</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="4">
+        <v>27825</v>
+      </c>
+      <c r="O6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="4">
+        <v>22530</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="4">
+        <v>18420</v>
+      </c>
+      <c r="S6" t="s">
+        <v>14</v>
+      </c>
+      <c r="T6" s="3">
+        <v>212175</v>
+      </c>
+      <c r="U6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="3">
+        <v>10270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4">
+        <v>48540</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>22610</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4">
+        <v>25925</v>
+      </c>
+      <c r="G7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="4">
+        <v>3845</v>
+      </c>
+      <c r="I7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4">
+        <v>3110</v>
+      </c>
+      <c r="K7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="4">
+        <v>4175</v>
+      </c>
+      <c r="M7" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="4">
+        <v>6880</v>
+      </c>
+      <c r="O7" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>9445</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>4</v>
+      </c>
+      <c r="R7" s="4">
+        <v>16605</v>
+      </c>
+      <c r="S7" t="s">
+        <v>4</v>
+      </c>
+      <c r="T7" s="4">
+        <v>48540</v>
+      </c>
+      <c r="U7" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="3">
+        <v>6360</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4">
+        <v>35830</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4">
+        <v>16540</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4">
+        <v>19700</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4">
+        <v>2600</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1875</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4">
+        <v>2685</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="4">
+        <v>5200</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="4">
+        <v>7690</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="4">
+        <v>14685</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="4">
+        <v>35830</v>
+      </c>
+      <c r="U8" t="s">
+        <v>7</v>
+      </c>
+      <c r="V8" s="3">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4">
+        <v>35205</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4">
+        <v>15505</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4">
+        <v>19285</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2520</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1870</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="4">
+        <v>2500</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="4">
+        <v>4295</v>
+      </c>
+      <c r="O9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="4">
+        <v>7470</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="4">
+        <v>13225</v>
+      </c>
+      <c r="S9" t="s">
+        <v>21</v>
+      </c>
+      <c r="T9" s="4">
+        <v>35205</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4">
+        <v>14140</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4">
+        <v>6415</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4">
+        <v>7725</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1390</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1410</v>
+      </c>
+      <c r="K10" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1700</v>
+      </c>
+      <c r="M10" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1985</v>
+      </c>
+      <c r="O10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P10" s="4">
+        <v>2745</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" s="4">
+        <v>4200</v>
+      </c>
+      <c r="S10" t="s">
+        <v>16</v>
+      </c>
+      <c r="T10" s="4">
+        <v>14140</v>
+      </c>
+      <c r="U10" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4">
+        <v>9195</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4">
+        <v>4990</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4">
+        <v>4205</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1305</v>
+      </c>
+      <c r="I11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1160</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="4">
+        <v>1215</v>
+      </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="5">
+        <v>830</v>
+      </c>
+      <c r="O11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="4">
+        <v>1070</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>17</v>
+      </c>
+      <c r="R11" s="4">
+        <v>2135</v>
+      </c>
+      <c r="S11" t="s">
+        <v>13</v>
+      </c>
+      <c r="T11" s="4">
+        <v>9195</v>
+      </c>
+      <c r="U11" t="s">
+        <v>15</v>
+      </c>
+      <c r="V11" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="4">
+        <v>5460</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2495</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2965</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="5">
+        <v>980</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1070</v>
+      </c>
+      <c r="K12" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="5">
+        <v>480</v>
+      </c>
+      <c r="M12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="5">
+        <v>645</v>
+      </c>
+      <c r="O12" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="5">
+        <v>455</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="5">
+        <v>970</v>
+      </c>
+      <c r="S12" t="s">
+        <v>17</v>
+      </c>
+      <c r="T12" s="4">
+        <v>5460</v>
+      </c>
+      <c r="U12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V12" s="3">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3335</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1980</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1420</v>
+      </c>
+      <c r="G13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="5">
+        <v>730</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="5">
+        <v>510</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="5">
+        <v>410</v>
+      </c>
+      <c r="M13" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="5">
+        <v>325</v>
+      </c>
+      <c r="O13" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="5">
+        <v>315</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>10</v>
+      </c>
+      <c r="R13" s="5">
+        <v>380</v>
+      </c>
+      <c r="S13" t="s">
+        <v>7</v>
+      </c>
+      <c r="T13" s="4">
+        <v>3335</v>
+      </c>
+      <c r="U13" t="s">
+        <v>21</v>
+      </c>
+      <c r="V13" s="3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2600</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1185</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1365</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="5">
+        <v>440</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="5">
+        <v>265</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="5">
+        <v>325</v>
+      </c>
+      <c r="M14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="4">
+        <v>305</v>
+      </c>
+      <c r="O14" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="4">
+        <v>210</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>15</v>
+      </c>
+      <c r="R14" s="5">
+        <v>195</v>
+      </c>
+      <c r="S14" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="4">
+        <v>2600</v>
+      </c>
+      <c r="U14" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1830</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="5">
+        <v>940</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="4">
+        <v>975</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="4">
+        <v>210</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="5">
+        <v>195</v>
+      </c>
+      <c r="K15" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="5">
+        <v>305</v>
+      </c>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+      <c r="N15" s="5">
+        <v>255</v>
+      </c>
+      <c r="O15" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="5">
+        <v>190</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>9</v>
+      </c>
+      <c r="R15" s="5">
+        <v>195</v>
+      </c>
+      <c r="S15" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" s="4">
+        <v>1780</v>
+      </c>
+      <c r="U15" t="s">
+        <v>17</v>
+      </c>
+      <c r="V15" s="3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1780</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4">
+        <v>865</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="5">
+        <v>845</v>
+      </c>
+      <c r="G16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="5">
+        <v>170</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4">
+        <v>190</v>
+      </c>
+      <c r="K16" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="5">
+        <v>215</v>
+      </c>
+      <c r="M16" t="s">
+        <v>5</v>
+      </c>
+      <c r="N16" s="5">
+        <v>250</v>
+      </c>
+      <c r="O16" t="s">
+        <v>20</v>
+      </c>
+      <c r="P16" s="5">
+        <v>125</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>13</v>
+      </c>
+      <c r="R16" s="5">
+        <v>175</v>
+      </c>
+      <c r="S16" t="s">
+        <v>5</v>
+      </c>
+      <c r="T16" s="4">
+        <v>1120</v>
+      </c>
+      <c r="U16" t="s">
+        <v>19</v>
+      </c>
+      <c r="V16" s="3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>615</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="5">
+        <v>530</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="5">
+        <v>145</v>
+      </c>
+      <c r="I17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <v>175</v>
+      </c>
+      <c r="K17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="5">
+        <v>145</v>
+      </c>
+      <c r="M17" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" s="5">
+        <v>140</v>
+      </c>
+      <c r="O17" t="s">
+        <v>12</v>
+      </c>
+      <c r="P17" s="5">
+        <v>125</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>12</v>
+      </c>
+      <c r="R17" s="5">
+        <v>170</v>
+      </c>
+      <c r="S17" t="s">
+        <v>20</v>
+      </c>
+      <c r="T17" s="4">
+        <v>1005</v>
+      </c>
+      <c r="U17" t="s">
+        <v>9</v>
+      </c>
+      <c r="V17" s="3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1005</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="5">
+        <v>540</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="5">
+        <v>515</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5">
+        <v>140</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="5">
+        <v>170</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="L18" s="5">
+        <v>120</v>
+      </c>
+      <c r="M18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" s="5">
+        <v>135</v>
+      </c>
+      <c r="O18" t="s">
+        <v>9</v>
+      </c>
+      <c r="P18" s="5">
+        <v>105</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="5">
+        <v>145</v>
+      </c>
+      <c r="S18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="4">
+        <v>1000</v>
+      </c>
+      <c r="U18" t="s">
+        <v>10</v>
+      </c>
+      <c r="V18" s="3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1000</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="5">
+        <v>485</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="5">
+        <v>500</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="5">
+        <v>130</v>
+      </c>
+      <c r="I19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="5">
+        <v>140</v>
+      </c>
+      <c r="K19" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" s="5">
+        <v>110</v>
+      </c>
+      <c r="M19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="5">
+        <v>130</v>
+      </c>
+      <c r="O19" t="s">
+        <v>7</v>
+      </c>
+      <c r="P19" s="5">
+        <v>100</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>7</v>
+      </c>
+      <c r="R19" s="5">
+        <v>105</v>
+      </c>
+      <c r="S19" t="s">
+        <v>10</v>
+      </c>
+      <c r="T19" s="5">
+        <v>970</v>
+      </c>
+      <c r="U19" t="s">
+        <v>8</v>
+      </c>
+      <c r="V19" s="3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="5">
+        <v>970</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="5">
+        <v>445</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="5">
+        <v>460</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="5">
+        <v>100</v>
+      </c>
+      <c r="I20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="5">
+        <v>65</v>
+      </c>
+      <c r="K20" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="5">
+        <v>95</v>
+      </c>
+      <c r="M20" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="5">
+        <v>90</v>
+      </c>
+      <c r="O20" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="5">
+        <v>95</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="5">
+        <v>65</v>
+      </c>
+      <c r="S20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" s="5">
+        <v>805</v>
+      </c>
+      <c r="U20" t="s">
+        <v>12</v>
+      </c>
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="5">
+        <v>805</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5">
+        <v>355</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5">
+        <v>445</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="5">
+        <v>45</v>
+      </c>
+      <c r="I21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="5">
+        <v>65</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="5">
+        <v>85</v>
+      </c>
+      <c r="M21" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" s="5">
+        <v>45</v>
+      </c>
+      <c r="O21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P21" s="5">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>11</v>
+      </c>
+      <c r="R21" s="5">
+        <v>55</v>
+      </c>
+      <c r="S21" t="s">
+        <v>15</v>
+      </c>
+      <c r="T21" s="4">
+        <v>570</v>
+      </c>
+      <c r="U21" t="s">
+        <v>20</v>
+      </c>
+      <c r="V21" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="5">
+        <v>345</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="5">
+        <v>175</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="5">
+        <v>175</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="5">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>11</v>
+      </c>
+      <c r="J22" s="5">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="5">
+        <v>50</v>
+      </c>
+      <c r="M22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="5">
+        <v>30</v>
+      </c>
+      <c r="O22" t="s">
+        <v>19</v>
+      </c>
+      <c r="P22" s="5">
+        <v>20</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="5">
+        <v>20</v>
+      </c>
+      <c r="S22" t="s">
+        <v>11</v>
+      </c>
+      <c r="T22" s="5">
+        <v>345</v>
+      </c>
+      <c r="U22" t="s">
+        <v>11</v>
+      </c>
+      <c r="V22" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="5">
+        <v>45</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="5">
+        <v>65</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="4">
+        <v>10</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="5">
+        <v>20</v>
+      </c>
+      <c r="M23" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23" s="5">
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23" s="5">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>19</v>
+      </c>
+      <c r="R23" s="5">
+        <v>15</v>
+      </c>
+      <c r="S23" t="s">
+        <v>18</v>
+      </c>
+      <c r="T23" s="4">
+        <v>110</v>
+      </c>
+      <c r="U23" t="s">
+        <v>18</v>
+      </c>
+      <c r="V23" s="3">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S5:T23">
+    <sortCondition descending="1" ref="T23"/>
+  </sortState>
+  <mergeCells count="12">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:A23">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A8:B8 A5:A7 A9:A23">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B23">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C23">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D4 C22:D22 C5:C21 C23">
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:D23">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E23">
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F4 E8:F8 E5:E7 E9:E23">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:F23">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G23">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:H23">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:H12 G5:G11 G20:H20 G13:G19 G21:G23">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I23">
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:J23">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22:J23 J8">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K23">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:L23">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M23">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:N23">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O23">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:P23">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q23">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:R23">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:S23">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:T23">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U23">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U4:V23">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E06FABA5-F3DF-4730-B55E-92A6E6ACA50C}">
+  <dimension ref="A1:V23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="22" width="18.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="15"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4">
+        <v>51785</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4">
+        <v>24745</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4">
+        <v>27040</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5850</v>
+      </c>
+      <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="4">
+        <v>7785</v>
+      </c>
+      <c r="K5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="4">
+        <v>6565</v>
+      </c>
+      <c r="M5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="4">
+        <v>7105</v>
+      </c>
+      <c r="O5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>9420</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="4">
+        <v>12630</v>
+      </c>
+      <c r="S5" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="4">
+        <v>48670</v>
+      </c>
+      <c r="U5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V5" s="3"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4">
+        <v>42830</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4">
+        <v>22390</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4">
+        <v>20445</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="4">
+        <v>5615</v>
+      </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4">
+        <v>4635</v>
+      </c>
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="4">
+        <v>5650</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="4">
+        <v>5135</v>
+      </c>
+      <c r="O6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="4">
+        <v>4110</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="4">
+        <v>5105</v>
+      </c>
+      <c r="S6" t="s">
+        <v>14</v>
+      </c>
+      <c r="T6" s="4">
+        <v>37615</v>
+      </c>
+      <c r="U6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="3"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4">
+        <v>14635</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6560</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8070</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1205</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="5">
+        <v>945</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="4">
+        <v>1175</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1825</v>
+      </c>
+      <c r="O7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2945</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>14</v>
+      </c>
+      <c r="R7" s="4">
+        <v>3615</v>
+      </c>
+      <c r="S7" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" s="4">
+        <v>14380</v>
+      </c>
+      <c r="U7" t="s">
+        <v>13</v>
+      </c>
+      <c r="V7" s="3"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4">
+        <v>6520</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3095</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3425</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5">
+        <v>765</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="5">
+        <v>415</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="5">
+        <v>545</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="5">
+        <v>785</v>
+      </c>
+      <c r="O8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1300</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2210</v>
+      </c>
+      <c r="S8" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" s="4">
+        <v>6335</v>
+      </c>
+      <c r="U8" t="s">
+        <v>7</v>
+      </c>
+      <c r="V8" s="3"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5025</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2250</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2770</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="5">
+        <v>630</v>
+      </c>
+      <c r="I9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="5">
+        <v>410</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="5">
+        <v>395</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="5">
+        <v>750</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1030</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="4">
+        <v>1725</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="4">
+        <v>4595</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4">
+        <v>4700</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2140</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2560</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="5">
+        <v>540</v>
+      </c>
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="5">
+        <v>390</v>
+      </c>
+      <c r="K10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="5">
+        <v>350</v>
+      </c>
+      <c r="M10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="5">
+        <v>625</v>
+      </c>
+      <c r="O10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="5">
+        <v>885</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="4">
+        <v>1350</v>
+      </c>
+      <c r="S10" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="4">
+        <v>4390</v>
+      </c>
+      <c r="U10" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1720</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5">
+        <v>985</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="5">
+        <v>735</v>
+      </c>
+      <c r="G11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5">
+        <v>510</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="5">
+        <v>315</v>
+      </c>
+      <c r="K11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="5">
+        <v>230</v>
+      </c>
+      <c r="M11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="5">
+        <v>200</v>
+      </c>
+      <c r="O11" t="s">
+        <v>16</v>
+      </c>
+      <c r="P11" s="5">
+        <v>125</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="5">
+        <v>185</v>
+      </c>
+      <c r="S11" t="s">
+        <v>16</v>
+      </c>
+      <c r="T11" s="5">
+        <v>775</v>
+      </c>
+      <c r="U11" t="s">
+        <v>15</v>
+      </c>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1245</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5">
+        <v>835</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4">
+        <v>495</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="5">
+        <v>480</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="5">
+        <v>265</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="5">
+        <v>140</v>
+      </c>
+      <c r="M12" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="5">
+        <v>200</v>
+      </c>
+      <c r="O12" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="5">
+        <v>120</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R12" s="5">
+        <v>155</v>
+      </c>
+      <c r="S12" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="5">
+        <v>415</v>
+      </c>
+      <c r="U12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1170</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="5">
+        <v>685</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5">
+        <v>485</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="5">
+        <v>430</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="5">
+        <v>260</v>
+      </c>
+      <c r="K13" t="s">
+        <v>5</v>
+      </c>
+      <c r="L13" s="5">
+        <v>130</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13" s="5">
+        <v>145</v>
+      </c>
+      <c r="O13" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="5">
+        <v>85</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>9</v>
+      </c>
+      <c r="R13" s="5">
+        <v>80</v>
+      </c>
+      <c r="S13" t="s">
+        <v>13</v>
+      </c>
+      <c r="T13" s="5">
+        <v>295</v>
+      </c>
+      <c r="U13" t="s">
+        <v>21</v>
+      </c>
+      <c r="V13" s="3"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4">
+        <v>955</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5">
+        <v>460</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5">
+        <v>435</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5">
+        <v>125</v>
+      </c>
+      <c r="I14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="5">
+        <v>80</v>
+      </c>
+      <c r="K14" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="5">
+        <v>95</v>
+      </c>
+      <c r="M14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="5">
+        <v>90</v>
+      </c>
+      <c r="O14" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="5">
+        <v>80</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="5">
+        <v>60</v>
+      </c>
+      <c r="S14" t="s">
+        <v>18</v>
+      </c>
+      <c r="T14" s="5">
+        <v>225</v>
+      </c>
+      <c r="U14" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5">
+        <v>750</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5">
+        <v>315</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="5">
+        <v>410</v>
+      </c>
+      <c r="G15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="5">
+        <v>120</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="5">
+        <v>75</v>
+      </c>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="5">
+        <v>55</v>
+      </c>
+      <c r="M15" t="s">
+        <v>7</v>
+      </c>
+      <c r="N15" s="5">
+        <v>70</v>
+      </c>
+      <c r="O15" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15" s="5">
+        <v>70</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" s="5">
+        <v>50</v>
+      </c>
+      <c r="S15" t="s">
+        <v>10</v>
+      </c>
+      <c r="T15" s="5">
+        <v>165</v>
+      </c>
+      <c r="U15" t="s">
+        <v>17</v>
+      </c>
+      <c r="V15" s="3"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5">
+        <v>485</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5">
+        <v>210</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5">
+        <v>280</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="5">
+        <v>75</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5">
+        <v>35</v>
+      </c>
+      <c r="K16" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="5">
+        <v>40</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="5">
+        <v>55</v>
+      </c>
+      <c r="O16" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="5">
+        <v>65</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>18</v>
+      </c>
+      <c r="R16" s="5">
+        <v>45</v>
+      </c>
+      <c r="S16" t="s">
+        <v>12</v>
+      </c>
+      <c r="T16" s="5">
+        <v>165</v>
+      </c>
+      <c r="U16" t="s">
+        <v>19</v>
+      </c>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5">
+        <v>350</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="4">
+        <v>180</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="5">
+        <v>180</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="4">
+        <v>55</v>
+      </c>
+      <c r="I17" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="5">
+        <v>30</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="5">
+        <v>35</v>
+      </c>
+      <c r="M17" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="5">
+        <v>35</v>
+      </c>
+      <c r="O17" t="s">
+        <v>15</v>
+      </c>
+      <c r="P17" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="5">
+        <v>40</v>
+      </c>
+      <c r="S17" t="s">
+        <v>15</v>
+      </c>
+      <c r="T17" s="4">
+        <v>110</v>
+      </c>
+      <c r="U17" t="s">
+        <v>9</v>
+      </c>
+      <c r="V17" s="3"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="5">
+        <v>325</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="5">
+        <v>145</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="4">
+        <v>175</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="5">
+        <v>40</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="5">
+        <v>30</v>
+      </c>
+      <c r="K18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="5">
+        <v>20</v>
+      </c>
+      <c r="M18" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="5">
+        <v>25</v>
+      </c>
+      <c r="O18" t="s">
+        <v>9</v>
+      </c>
+      <c r="P18" s="5">
+        <v>35</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="5">
+        <v>35</v>
+      </c>
+      <c r="S18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="5">
+        <v>100</v>
+      </c>
+      <c r="U18" t="s">
+        <v>10</v>
+      </c>
+      <c r="V18" s="3"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5">
+        <v>245</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="5">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="5">
+        <v>140</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="5">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="4">
+        <v>25</v>
+      </c>
+      <c r="K19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="5">
+        <v>15</v>
+      </c>
+      <c r="M19" t="s">
+        <v>9</v>
+      </c>
+      <c r="N19" s="5">
+        <v>15</v>
+      </c>
+      <c r="O19" t="s">
+        <v>7</v>
+      </c>
+      <c r="P19" s="5">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R19" s="5">
+        <v>20</v>
+      </c>
+      <c r="S19" t="s">
+        <v>7</v>
+      </c>
+      <c r="T19" s="5">
+        <v>90</v>
+      </c>
+      <c r="U19" t="s">
+        <v>8</v>
+      </c>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="5">
+        <v>175</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="5">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5">
+        <v>10</v>
+      </c>
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="5">
+        <v>20</v>
+      </c>
+      <c r="K20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="5">
+        <v>15</v>
+      </c>
+      <c r="M20" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="5">
+        <v>15</v>
+      </c>
+      <c r="O20" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>7</v>
+      </c>
+      <c r="R20" s="5">
+        <v>15</v>
+      </c>
+      <c r="S20" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="5">
+        <v>80</v>
+      </c>
+      <c r="U20" t="s">
+        <v>12</v>
+      </c>
+      <c r="V20" s="3"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="5">
+        <v>165</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="5">
+        <v>85</v>
+      </c>
+      <c r="G21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="5">
+        <v>10</v>
+      </c>
+      <c r="I21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="5">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="5">
+        <v>15</v>
+      </c>
+      <c r="M21" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="5">
+        <v>10</v>
+      </c>
+      <c r="O21" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" s="5">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>20</v>
+      </c>
+      <c r="T21" s="4">
+        <v>75</v>
+      </c>
+      <c r="U21" t="s">
+        <v>20</v>
+      </c>
+      <c r="V21" s="3"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="5">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="5">
+        <v>45</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="5">
+        <v>10</v>
+      </c>
+      <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>11</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>11</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" s="4">
+        <v>10</v>
+      </c>
+      <c r="U22" t="s">
+        <v>11</v>
+      </c>
+      <c r="V22" s="3"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="5">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="5">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>19</v>
+      </c>
+      <c r="P23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>19</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0</v>
+      </c>
+      <c r="S23" t="s">
+        <v>11</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0</v>
+      </c>
+      <c r="U23" t="s">
+        <v>18</v>
+      </c>
+      <c r="V23" s="3"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="S5:T23">
+    <sortCondition descending="1" ref="T23"/>
+  </sortState>
+  <mergeCells count="12">
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:A23">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:B4 A5:A23">
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:B23">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B6 B10:B13 B15 B21">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:C23">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D4 C22:D22 C5:C21 C23">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:D23 C5:C6">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:D18 C20:D20 C19 C22:D22 C21 C23 C5:C15">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:D23">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E23">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F4 E5:E23">
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F23">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:F10 E5:E9 E15:F15 E11:E14 E22:F23 E16:E21">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G23">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:H5 G15:H22 G6:G14 G23">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:H23">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20:H20 G5:G19 G21:G23">
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I23">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:J23">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:J17 I5:I15 I19:J23 I18">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22:J23">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K23">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="65">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:L23 K5">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13:L13 K5:K12 K15:L15 K14 K17:L23 K16">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M14 M15:N23">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M23">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="57">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:N23">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O23">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O14:P16 O5:O13 O21:P23 O17:O20">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q23">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q14:R14 Q5:Q13 Q17:R17 Q15:Q16 Q21:R23 Q18:Q20">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:S23">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S15:T15 S5:S14 S18:T18 S16:S17 S22:T22 S19:S21 S23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U23">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U4:V23">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:L23">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:L23">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O5:P23">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:R23">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S4:T23">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>